--- a/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos</t>
+          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,03; 26,75</t>
+          <t>19,12; 26,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 25,54</t>
+          <t>18,95; 25,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 24,14</t>
+          <t>15,14; 24,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 26,73</t>
+          <t>7,47; 26,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,82; 23,32</t>
+          <t>16,66; 23,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 25,17</t>
+          <t>17,44; 25,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,96; 20,06</t>
+          <t>14,98; 20,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,57</t>
+          <t>3,78; 8,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 23,62</t>
+          <t>18,6; 23,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,08; 24,14</t>
+          <t>19,19; 24,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,47; 20,46</t>
+          <t>15,61; 21,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 14,89</t>
+          <t>6,17; 15,63</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 24,32</t>
+          <t>21,02; 24,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,98; 21,74</t>
+          <t>19,04; 21,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,94; 18,96</t>
+          <t>16,08; 19,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,94; 25,15</t>
+          <t>13,92; 25,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,36; 22,96</t>
+          <t>20,35; 23,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 22,51</t>
+          <t>19,62; 22,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 18,76</t>
+          <t>16,01; 18,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 19,89</t>
+          <t>12,55; 20,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,03; 23,06</t>
+          <t>21,01; 23,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 21,56</t>
+          <t>19,6; 21,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 18,33</t>
+          <t>16,31; 18,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,76; 20,3</t>
+          <t>13,94; 20,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 21,2</t>
+          <t>18,1; 21,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 21,28</t>
+          <t>16,44; 21,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 17,74</t>
+          <t>14,29; 17,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,39; 22,47</t>
+          <t>12,52; 22,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,04; 24,15</t>
+          <t>18,91; 24,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 21,4</t>
+          <t>16,88; 21,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,91</t>
+          <t>14,53; 21,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 47,16</t>
+          <t>15,55; 47,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 22,0</t>
+          <t>19,02; 21,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,19; 20,59</t>
+          <t>17,17; 20,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,96; 18,99</t>
+          <t>14,96; 18,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 32,78</t>
+          <t>15,41; 30,86</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,59; 23,11</t>
+          <t>20,53; 23,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,05; 21,31</t>
+          <t>18,99; 21,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 18,19</t>
+          <t>16,1; 18,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,95</t>
+          <t>14,05; 22,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,18; 22,38</t>
+          <t>20,19; 22,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 21,49</t>
+          <t>19,29; 21,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 18,61</t>
+          <t>16,07; 18,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,99</t>
+          <t>13,64; 23,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 22,33</t>
+          <t>20,65; 22,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 20,98</t>
+          <t>19,41; 20,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 17,97</t>
+          <t>16,26; 17,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 20,61</t>
+          <t>14,53; 20,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 26,53</t>
+          <t>19,03; 26,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,95; 25,61</t>
+          <t>19,07; 25,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 24,82</t>
+          <t>14,88; 24,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 26,74</t>
+          <t>7,15; 25,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,04</t>
+          <t>16,81; 23,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 25,21</t>
+          <t>17,5; 25,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,98; 20,49</t>
+          <t>14,94; 20,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,59</t>
+          <t>4,08; 8,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,6; 23,39</t>
+          <t>18,51; 23,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,19; 24,25</t>
+          <t>19,05; 23,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,26</t>
+          <t>15,66; 20,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,63</t>
+          <t>6,3; 16,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 24,36</t>
+          <t>20,96; 24,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,04; 21,83</t>
+          <t>18,93; 21,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,08; 19,0</t>
+          <t>15,96; 18,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 25,41</t>
+          <t>14,02; 25,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,35; 23,09</t>
+          <t>20,33; 22,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,62; 22,4</t>
+          <t>19,57; 22,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,7</t>
+          <t>16,03; 18,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 20,47</t>
+          <t>12,54; 20,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,01; 23,14</t>
+          <t>20,97; 23,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 21,59</t>
+          <t>19,64; 21,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 18,43</t>
+          <t>16,35; 18,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,94; 20,21</t>
+          <t>13,7; 20,03</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 21,27</t>
+          <t>18,07; 21,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 21,36</t>
+          <t>16,52; 21,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,82</t>
+          <t>14,45; 17,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,52; 22,56</t>
+          <t>12,0; 21,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,91; 24,13</t>
+          <t>19,05; 24,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,88; 21,42</t>
+          <t>16,56; 21,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 21,23</t>
+          <t>14,54; 21,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,55; 47,69</t>
+          <t>15,1; 46,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,02; 21,93</t>
+          <t>19,13; 22,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 20,32</t>
+          <t>17,03; 20,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,96; 18,88</t>
+          <t>14,87; 18,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,41; 30,86</t>
+          <t>15,31; 33,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,53; 23,06</t>
+          <t>20,58; 23,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 21,2</t>
+          <t>19,01; 21,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,1; 18,37</t>
+          <t>16,06; 18,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,05; 22,45</t>
+          <t>14,3; 22,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 22,43</t>
+          <t>20,03; 22,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,29; 21,58</t>
+          <t>19,21; 21,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,07; 18,57</t>
+          <t>16,01; 18,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 23,75</t>
+          <t>13,63; 22,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,65; 22,31</t>
+          <t>20,64; 22,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 20,97</t>
+          <t>19,58; 21,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,26; 17,96</t>
+          <t>16,31; 17,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,53; 20,56</t>
+          <t>14,55; 20,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que tuvieron que esperar hasta ser atendidos por el médico en minutos (tasa de respuesta: 91,62%)</t>
+          <t>Tiempo medio en minutos que tuvieron que esperar desde que llegaron hasta ser atendidos/as en la última consulta médica (tasa de respuesta: 91,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,49</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>22,17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18,08</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,59</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>13,76</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,93</t>
+          <t>9,37</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,03; 26,05</t>
+          <t>16,82; 23,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 25,45</t>
+          <t>17,64; 25,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 24,43</t>
+          <t>14,96; 20,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 25,61</t>
+          <t>3,66; 8,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,06</t>
+          <t>19,03; 26,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,5; 25,27</t>
+          <t>19,01; 25,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,14</t>
+          <t>15,1; 24,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,6</t>
+          <t>7,37; 30,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 23,47</t>
+          <t>18,62; 23,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 23,8</t>
+          <t>19,08; 24,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,66; 20,91</t>
+          <t>15,47; 20,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 16,1</t>
+          <t>6,46; 16,49</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,89</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,3</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15,18</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>20,28</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,26</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,75</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,55</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,89</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,3</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,24</t>
+          <t>17,41</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,32</t>
+          <t>16,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,96; 24,54</t>
+          <t>20,36; 22,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 21,67</t>
+          <t>19,74; 22,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 18,76</t>
+          <t>16,07; 18,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,02; 25,45</t>
+          <t>12,25; 20,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 22,97</t>
+          <t>20,84; 24,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,57; 22,4</t>
+          <t>18,98; 21,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,03; 18,81</t>
+          <t>15,94; 18,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,67</t>
+          <t>13,81; 24,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,97; 23,03</t>
+          <t>21,03; 23,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 21,6</t>
+          <t>19,64; 21,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,35; 18,49</t>
+          <t>16,28; 18,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,7; 20,03</t>
+          <t>13,71; 19,91</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,66</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,64</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25,58</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18,63</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>15,93</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,26</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,66</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,64</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,01</t>
+          <t>15,28</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,87</t>
+          <t>20,66</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 21,45</t>
+          <t>19,04; 24,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 21,55</t>
+          <t>16,84; 21,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,84</t>
+          <t>14,56; 20,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 21,72</t>
+          <t>15,32; 49,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,05; 24,13</t>
+          <t>18,0; 21,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,09</t>
+          <t>16,64; 21,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,54; 21,66</t>
+          <t>14,38; 17,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 46,23</t>
+          <t>11,89; 21,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,13; 22,05</t>
+          <t>19,15; 22,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,03; 20,41</t>
+          <t>17,19; 20,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,87; 18,66</t>
+          <t>14,96; 18,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,31; 33,07</t>
+          <t>15,31; 33,02</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,34</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17,11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17,07</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21,68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,02</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,99</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,22</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,98</t>
+          <t>16,86</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,58; 23,14</t>
+          <t>20,18; 22,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 21,25</t>
+          <t>19,21; 21,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,27</t>
+          <t>15,97; 18,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,63</t>
+          <t>13,8; 23,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,03; 22,46</t>
+          <t>20,59; 23,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 21,46</t>
+          <t>19,05; 21,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,51</t>
+          <t>15,98; 18,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,59</t>
+          <t>13,84; 20,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 22,26</t>
+          <t>20,64; 22,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 21,06</t>
+          <t>19,41; 20,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 17,96</t>
+          <t>16,32; 17,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,73</t>
+          <t>14,58; 20,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ18D_M-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>19,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,81</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,08</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,76</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20,7</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21,24</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17,6</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,37</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>19.26326037756701</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>20.54787081865104</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.10877017109047</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.494098269183123</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>22.16945401806376</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>21.81408198315016</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>18.08325346380962</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>13.7639430828427</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>20.70208731663572</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>21.236010008514</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>17.59904863597333</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.371164260190355</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16,82; 23,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17,64; 25,17</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14,96; 20,06</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,66; 8,63</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>19,03; 26,75</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,01; 25,54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,1; 24,14</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 30,23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18,62; 23,62</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19,08; 24,14</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15,47; 20,46</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>6,46; 16,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>16.82333052355406</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>17.64074134652253</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>14.9619069685848</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>3.662053582488678</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>19.03235389894412</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>19.00839600909903</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>15.09653044169727</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.373061672638169</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>18.62415009482978</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>19.08040549219164</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>15.47457896756052</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>6.462869894457765</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>23.32113363105795</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>25.17248593769402</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20.05500440669694</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.634383945497659</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>26.74592693977539</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>25.54368980571406</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>24.14491140273712</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>30.23213469835244</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>23.61978242675031</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>24.14228705839875</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>20.46451706020279</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>16.4924465466004</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>21,55</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>20,89</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,3</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,18</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,41</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,28</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,26</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21,96</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20,6</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17,28</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>20,36; 22,96</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19,74; 22,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16,07; 18,76</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12,25; 20,1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20,84; 24,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,98; 21,74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,94; 18,96</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13,81; 24,11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21,03; 23,06</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19,64; 21,56</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16,28; 18,33</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,71; 19,91</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>21.54990530950397</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>20.88889126365379</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>17.30275909003037</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>15.1841549086065</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>22.41447197236145</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>20.28022686984427</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>17.25589924722593</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>17.40595913250933</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>21.96402602887767</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>20.59979313823159</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>17.2791519708463</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>16.1695880584961</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>21,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18,66</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,62</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,63</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,93</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15,28</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20,43</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18,64</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16,31</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>20,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>20.36076409153278</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>19.74471162955902</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>16.07181140671923</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>12.25361256888443</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>20.84160460190855</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>18.98395966570463</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>15.9419588562789</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>13.81202774585953</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>21.02768583600126</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>19.63898457098828</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>16.27516082886548</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>13.71034182233225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>19,04; 24,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>16,84; 21,4</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>14,56; 20,91</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15,32; 49,53</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,0; 21,2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>16,64; 21,28</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>14,38; 17,74</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>11,89; 21,31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19,15; 22,0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17,19; 20,59</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14,96; 18,99</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>15,31; 33,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>22.96199070583553</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.5106455187259</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>18.75910285821307</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>20.09878410535584</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>24.31632196254495</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>21.74257020329043</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>18.95636539899417</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>24.10846742439105</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>23.05577746573076</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>21.56136821208428</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>18.32850331548575</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>19.90740516880875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>21,22</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20,34</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,07</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,68</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,02</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16,59</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21,44</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20,22</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17,07</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,86</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>21.25834069130986</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>18.65912106557178</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>16.64101722761502</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>25.58229069364413</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>19.61881790359498</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>18.62603814328642</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>15.92674272180633</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>15.2807033456553</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>20.42570801045644</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>18.64295973835697</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>16.31295657702331</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>20.66423917473676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>20,18; 22,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19,21; 21,49</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,97; 18,61</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13,8; 23,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,59; 23,11</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,05; 21,31</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,98; 18,19</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13,84; 20,95</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20,64; 22,33</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19,41; 20,98</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16,32; 17,97</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,58; 20,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>19.03980615700486</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>16.83946636635802</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>14.56083018001342</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>15.31637498511699</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>17.99849631830314</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>16.63799478305639</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>14.38348683243508</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>11.88988942627196</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>19.14731574388284</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>17.18825131423614</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>14.96055457683001</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>15.30700340838472</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>24.1517180899003</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>21.40310186308707</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>20.91180787312384</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>49.53082557286457</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>21.19826206290833</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>21.27621431428621</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>17.74109421795639</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>21.30852193730804</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>21.99820953887873</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>20.58592546987244</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>18.98791140573328</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>33.01609442406452</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>21.21724130139805</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>20.34148018849652</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>17.10992561735796</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>17.07415936286198</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>21.68045002578471</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>20.10049855844353</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>17.02227172167003</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>16.58984697811489</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>21.44322804342774</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>20.22431250037274</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>17.06674495947114</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>16.856725395439</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>20.18162005015559</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>19.21149634983406</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>15.96789560650419</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>13.80329169288218</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>20.58500862176672</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>19.05194290084968</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>15.97721124196729</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>13.84105478791669</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>20.63813951761756</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>19.4098567691475</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>16.31656524892515</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>14.58252901200152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>22.38258588906818</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.49068238455248</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>18.61264151134981</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>23.49436494382347</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>23.11160996594476</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>21.31238342408531</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>18.18597390600504</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>20.95348885620419</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>22.32913396768894</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>20.98125618149792</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>17.9723657073723</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>20.2898407291083</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
